--- a/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
+++ b/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P.388</t>
+    <t>P388</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
+++ b/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>17:00 28/03/2020</t>
+    <t>17:00 28/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>02:30 30/03/2020</t>
+    <t>02:30 30/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -96,11 +96,11 @@
   </si>
   <si>
     <t xml:space="preserve">16:30
-28/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:00
-28/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t/>
@@ -113,7 +113,7 @@
   </si>
   <si>
     <t xml:space="preserve">18:30
-28/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>Lái máy nghỉ ăn cơm</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">22:53
-28/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:20
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>giao ca sáng-đêm</t>
@@ -149,7 +149,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:45
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -159,7 +159,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:20
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -169,7 +169,7 @@
   </si>
   <si>
     <t xml:space="preserve">19:59
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:41
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -189,7 +189,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:47
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -199,7 +199,7 @@
   </si>
   <si>
     <t xml:space="preserve">22:05
-29/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -209,7 +209,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:30
-30/03/2020</t>
+28/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
+++ b/SGC-CKN/Excel/36fb37bf-1fce-45d3-94a0-2058268eb21b_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P_388_D1200_30-03-2020.xlsx
@@ -1478,16 +1478,16 @@
         <v>-56.64</v>
       </c>
       <c r="G18" s="29">
-        <v>-50.5</v>
+        <v>-60.5</v>
       </c>
       <c r="H18" s="29">
         <v>0.7</v>
       </c>
       <c r="I18" s="29">
-        <v>6.14</v>
+        <v>3.86</v>
       </c>
       <c r="J18" s="8">
-        <v>8.77</v>
+        <v>5.51</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>29</v>
@@ -1510,10 +1510,10 @@
         <v>55</v>
       </c>
       <c r="F19" s="32">
-        <v>-50.5</v>
+        <v>-60.5</v>
       </c>
       <c r="G19" s="32">
-        <v>-55.2</v>
+        <v>-65.2</v>
       </c>
       <c r="H19" s="32">
         <v>1.1</v>
@@ -1545,7 +1545,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="35">
-        <v>-55.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G20" s="35">
         <v>-68.3</v>
@@ -1554,10 +1554,10 @@
         <v>0.3</v>
       </c>
       <c r="I20" s="35">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J20" s="8">
-        <v>43.67</v>
+        <v>10.33</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>29</v>
@@ -1953,16 +1953,16 @@
         <v>-56.64</v>
       </c>
       <c r="F9" s="29">
-        <v>-50.5</v>
+        <v>-60.5</v>
       </c>
       <c r="G9" s="29">
         <v>0.7</v>
       </c>
       <c r="H9" s="29">
-        <v>6.14</v>
+        <v>3.86</v>
       </c>
       <c r="I9" s="8">
-        <v>8.77</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1979,10 +1979,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="32">
-        <v>-50.5</v>
+        <v>-60.5</v>
       </c>
       <c r="F10" s="32">
-        <v>-55.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G10" s="32">
         <v>1.1</v>
@@ -2008,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="35">
-        <v>-55.2</v>
+        <v>-65.2</v>
       </c>
       <c r="F11" s="35">
         <v>-68.3</v>
@@ -2017,10 +2017,10 @@
         <v>0.3</v>
       </c>
       <c r="H11" s="35">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="I11" s="8">
-        <v>43.67</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2075,10 +2075,10 @@
         <v>34</v>
       </c>
       <c r="H13" s="40">
-        <v>87.78</v>
+        <v>75.5</v>
       </c>
       <c r="I13" s="40">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>
